--- a/astro-site/public/dl/guia-restaurante-casual/calculadora-ticket-medio.xlsx
+++ b/astro-site/public/dl/guia-restaurante-casual/calculadora-ticket-medio.xlsx
@@ -496,9 +496,9 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -518,6 +518,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -546,10 +547,19 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Celdas verdes = campos editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/guia-restaurante-casual · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -558,7 +568,16 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -567,7 +586,7 @@
   <sheetPr>
     <tabColor rgb="0000BCD4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -590,6 +609,8 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -680,6 +701,7 @@
         <v>2</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
@@ -693,7 +715,16 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -702,7 +733,7 @@
   <sheetPr>
     <tabColor rgb="00FFC107"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -725,6 +756,8 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
@@ -753,7 +786,7 @@
       </c>
       <c r="B7" s="11">
         <f>B5*B6</f>
-        <v/>
+        <v>4.62</v>
       </c>
     </row>
     <row r="8">
@@ -784,7 +817,7 @@
       </c>
       <c r="B10" s="11">
         <f>B5*B8*B9</f>
-        <v/>
+        <v>9240.0</v>
       </c>
     </row>
   </sheetData>
@@ -792,6 +825,15 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>